--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/LOUISIANA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/LOUISIANA_2021.xlsx
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C170">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C178">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C399">
